--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aneesha\Documents\UiPath\Gulf Drug Process\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E72017-9011-4903-A936-A8399B173036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -90,15 +91,15 @@
   </si>
   <si>
     <t>Orchestrator queue Name. The value must match with the queue name defined on Orchestrator.</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Logging field which allows grouping of log data of two or more subprocesses under the same business process name</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>OrchestratorQueueName</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Must be 0 if working with Orchestrator queues. If &gt; 0, the robot will retry the same transaction which failed with a system exception. Must be an integer value.</t>
@@ -335,48 +336,6 @@
     <t>Error_SS_Path</t>
   </si>
   <si>
-    <t>C:\Users\Aneesha\Documents\UiPath\Gulf Drug Process\Data\Logs\Process Log\</t>
-  </si>
-  <si>
-    <t>C:\Users\Aneesha\Documents\UiPath\Gulf Drug Process\Data\Input\</t>
-  </si>
-  <si>
-    <t>C:\Users\Aneesha\Documents\UiPath\Gulf Drug Process\Data\Output\</t>
-  </si>
-  <si>
-    <t>C:\Users\Aneesha\Documents\UiPath\Gulf Drug Process\Data\Staging\</t>
-  </si>
-  <si>
-    <t>C:\Users\Aneesha\Documents\UiPath\Gulf Drug Process\Data\Attachment Folder\</t>
-  </si>
-  <si>
-    <t>C:\Users\Aneesha\Documents\UiPath\Gulf Drug Process\Data\Mail Templates\BussinessException_Mail_Template.txt</t>
-  </si>
-  <si>
-    <t>C:\Users\Aneesha\Documents\UiPath\Gulf Drug Process\Data\Mail Templates\SytemException_Mail_Template.txt</t>
-  </si>
-  <si>
-    <t>C:\Users\Aneesha\Documents\UiPath\Gulf Drug Process\Data\Mail Templates\Success_Mail_Template.txt</t>
-  </si>
-  <si>
-    <t>C:\Users\Aneesha\Documents\UiPath\Gulf Drug Process\Exceptions_Screenshots\</t>
-  </si>
-  <si>
-    <t>C:\Users\Aneesha\Documents\UiPath\Gulf Drug Process\Data\Output\Bussiness Exceptions_Screenshots\</t>
-  </si>
-  <si>
-    <t>C:\Users\Aneesha\Documents\UiPath\Gulf Drug Process\Data\Output\Success\</t>
-  </si>
-  <si>
-    <t>C:\Users\Aneesha\Documents\UiPath\Gulf Drug Process\Data\Output\Failed\</t>
-  </si>
-  <si>
-    <t>mohamedalthaf@atominosconsulting.com</t>
-  </si>
-  <si>
-    <t>Althaf@123</t>
-  </si>
-  <si>
     <t>CC_Address</t>
   </si>
   <si>
@@ -386,18 +345,67 @@
     <t>Project_Name</t>
   </si>
   <si>
-    <t>mohamedalthaf9399@outlook.com</t>
+    <t>C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\Logs\Process Log\</t>
+  </si>
+  <si>
+    <t>C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\Input\</t>
+  </si>
+  <si>
+    <t>C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\Output\</t>
+  </si>
+  <si>
+    <t>C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\Staging\</t>
+  </si>
+  <si>
+    <t>C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\Attachment Folder\</t>
+  </si>
+  <si>
+    <t>C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\Mail Templates\BussinessException_Mail_Template.txt</t>
+  </si>
+  <si>
+    <t>C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\Mail Templates\SytemException_Mail_Template.txt</t>
+  </si>
+  <si>
+    <t>C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\Mail Templates\Success_Mail_Template.txt</t>
+  </si>
+  <si>
+    <t>C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Exceptions_Screenshots\</t>
+  </si>
+  <si>
+    <t>C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\Output\Bussiness Exceptions_Screenshots\</t>
+  </si>
+  <si>
+    <t>C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\Output\Success\</t>
+  </si>
+  <si>
+    <t>C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\Output\Failed\</t>
+  </si>
+  <si>
+    <t>ramanathan@atominosconsulting.com</t>
+  </si>
+  <si>
+    <t>Atominos@123456</t>
+  </si>
+  <si>
+    <t>rohinkumar@atominosconsulting.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -451,24 +459,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -782,14 +792,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1017"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="43.5546875" customWidth="1"/>
-    <col min="2" max="2" width="166.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.44140625" customWidth="1"/>
-    <col min="4" max="26" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="43.5703125" customWidth="1"/>
+    <col min="2" max="2" width="166.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.42578125" customWidth="1"/>
+    <col min="4" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -837,7 +847,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="43.2">
+    <row r="3" spans="1:26" ht="45">
       <c r="A3" s="2" t="s">
         <v>31</v>
       </c>
@@ -846,7 +856,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="28.8">
+    <row r="4" spans="1:26" ht="30">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -857,7 +867,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="14.4">
+    <row r="5" spans="1:26">
       <c r="A5" s="2" t="s">
         <v>93</v>
       </c>
@@ -866,52 +876,52 @@
       </c>
       <c r="C5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="14.4">
+    <row r="6" spans="1:26">
       <c r="A6" s="2" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="14.4">
+    <row r="7" spans="1:26">
       <c r="A7" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B7" t="s">
-        <v>115</v>
+      <c r="B7" s="9" t="s">
+        <v>118</v>
       </c>
       <c r="C7" s="4"/>
     </row>
-    <row r="8" spans="1:26" ht="14.4">
+    <row r="8" spans="1:26">
       <c r="A8" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B8" t="s">
-        <v>116</v>
+      <c r="B8" s="10" t="s">
+        <v>119</v>
       </c>
       <c r="C8" s="4"/>
     </row>
-    <row r="9" spans="1:26" ht="14.4">
+    <row r="9" spans="1:26">
       <c r="A9" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C9" s="4"/>
     </row>
-    <row r="10" spans="1:26" ht="14.4">
+    <row r="10" spans="1:26">
       <c r="A10" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="10" t="s">
         <v>120</v>
       </c>
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:26" ht="14.4">
+    <row r="11" spans="1:26">
       <c r="A11" s="2" t="s">
         <v>90</v>
       </c>
@@ -920,7 +930,7 @@
       </c>
       <c r="C11" s="4"/>
     </row>
-    <row r="12" spans="1:26" ht="14.4">
+    <row r="12" spans="1:26">
       <c r="A12" s="2" t="s">
         <v>91</v>
       </c>
@@ -929,12 +939,12 @@
       </c>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:26" ht="14.4">
+    <row r="13" spans="1:26">
       <c r="A13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C13" s="4"/>
     </row>
@@ -961,7 +971,7 @@
         <v>46</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C16" s="2"/>
     </row>
@@ -970,7 +980,7 @@
         <v>56</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C17" s="2"/>
     </row>
@@ -979,7 +989,7 @@
         <v>84</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C18" s="2"/>
     </row>
@@ -988,7 +998,7 @@
         <v>73</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C19" s="2"/>
     </row>
@@ -997,7 +1007,7 @@
         <v>95</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C20" s="2"/>
     </row>
@@ -1015,7 +1025,7 @@
         <v>96</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C22" s="2"/>
     </row>
@@ -1033,7 +1043,7 @@
         <v>99</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C24" s="2"/>
     </row>
@@ -1078,7 +1088,7 @@
         <v>102</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C29" s="2"/>
     </row>
@@ -1087,7 +1097,7 @@
         <v>57</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C30" s="2"/>
     </row>
@@ -1096,7 +1106,7 @@
         <v>58</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C31" s="2"/>
     </row>
@@ -1114,7 +1124,7 @@
         <v>59</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C33" s="2"/>
     </row>
@@ -2177,21 +2187,21 @@
     <row r="1016" ht="14.25" customHeight="1"/>
     <row r="1017" ht="14.25" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z988"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="3" max="3" width="75.44140625" customWidth="1"/>
-    <col min="4" max="26" width="8.6640625" customWidth="1"/>
+    <col min="3" max="3" width="75.42578125" customWidth="1"/>
+    <col min="4" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -2228,7 +2238,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="28.8">
+    <row r="2" spans="1:26" ht="30">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -2239,7 +2249,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="43.2">
+    <row r="3" spans="1:26" ht="45">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -2353,7 +2363,7 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="17" spans="1:3" ht="28.8">
+    <row r="17" spans="1:3" ht="45">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -3336,20 +3346,20 @@
     <row r="987" ht="14.25" customHeight="1"/>
     <row r="988" ht="14.25" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.88671875" customWidth="1"/>
-    <col min="2" max="2" width="30.109375" customWidth="1"/>
-    <col min="3" max="3" width="60.33203125" customWidth="1"/>
-    <col min="4" max="26" width="65.44140625" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" customWidth="1"/>
+    <col min="3" max="3" width="60.28515625" customWidth="1"/>
+    <col min="4" max="26" width="65.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -4388,7 +4398,7 @@
     <row r="999" ht="14.25" customHeight="1"/>
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E72017-9011-4903-A936-A8399B173036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D407B5D1-C988-46E7-9BBE-51F98F9C0ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -459,7 +459,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -478,7 +478,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -898,7 +897,7 @@
       <c r="A8" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" t="s">
         <v>119</v>
       </c>
       <c r="C8" s="4"/>
@@ -916,7 +915,7 @@
       <c r="A10" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" t="s">
         <v>120</v>
       </c>
       <c r="C10" s="4"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D407B5D1-C988-46E7-9BBE-51F98F9C0ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495AA207-204E-46F4-AE24-621C984D1F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="125">
   <si>
     <t>Name</t>
   </si>
@@ -342,9 +342,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>Project_Name</t>
-  </si>
-  <si>
     <t>C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\Logs\Process Log\</t>
   </si>
   <si>
@@ -388,6 +385,21 @@
   </si>
   <si>
     <t>rohinkumar@atominosconsulting.com</t>
+  </si>
+  <si>
+    <t>Missing_Status_path</t>
+  </si>
+  <si>
+    <t>C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\Output\Missing\</t>
+  </si>
+  <si>
+    <t>Missing_Status_SheetName</t>
+  </si>
+  <si>
+    <t>Gulfdrug_Missing</t>
+  </si>
+  <si>
+    <t>Process_Name</t>
   </si>
 </sst>
 </file>
@@ -792,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1017"/>
+  <dimension ref="A1:Z1019"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
@@ -877,7 +889,7 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="2" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>92</v>
@@ -889,7 +901,7 @@
         <v>86</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C7" s="4"/>
     </row>
@@ -898,7 +910,7 @@
         <v>87</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8" s="4"/>
     </row>
@@ -916,7 +928,7 @@
         <v>88</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C10" s="4"/>
     </row>
@@ -943,7 +955,7 @@
         <v>62</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C13" s="4"/>
     </row>
@@ -970,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C16" s="2"/>
     </row>
@@ -979,7 +991,7 @@
         <v>56</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C17" s="2"/>
     </row>
@@ -988,7 +1000,7 @@
         <v>84</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C18" s="2"/>
     </row>
@@ -997,7 +1009,7 @@
         <v>73</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C19" s="2"/>
     </row>
@@ -1006,7 +1018,7 @@
         <v>95</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C20" s="2"/>
     </row>
@@ -1024,7 +1036,7 @@
         <v>96</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C22" s="2"/>
     </row>
@@ -1042,7 +1054,7 @@
         <v>99</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C24" s="2"/>
     </row>
@@ -1087,7 +1099,7 @@
         <v>102</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C29" s="2"/>
     </row>
@@ -1096,7 +1108,7 @@
         <v>57</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C30" s="2"/>
     </row>
@@ -1105,7 +1117,7 @@
         <v>58</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C31" s="2"/>
     </row>
@@ -1123,7 +1135,7 @@
         <v>59</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C33" s="2"/>
     </row>
@@ -1138,81 +1150,97 @@
     </row>
     <row r="35" spans="1:3" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="C35" s="2"/>
     </row>
     <row r="36" spans="1:3" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>66</v>
+        <v>122</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="C36" s="2"/>
     </row>
     <row r="37" spans="1:3" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B37" t="s">
-        <v>67</v>
+        <v>63</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C37" s="2"/>
     </row>
     <row r="38" spans="1:3" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="C38" s="2"/>
     </row>
     <row r="39" spans="1:3" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>77</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="B39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" s="2"/>
     </row>
     <row r="40" spans="1:3" ht="14.25" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A44" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A45" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B45" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="45" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="46" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="47" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="48" spans="1:3" ht="14.25" customHeight="1"/>
@@ -2185,6 +2213,8 @@
     <row r="1015" ht="14.25" customHeight="1"/>
     <row r="1016" ht="14.25" customHeight="1"/>
     <row r="1017" ht="14.25" customHeight="1"/>
+    <row r="1018" ht="14.25" customHeight="1"/>
+    <row r="1019" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495AA207-204E-46F4-AE24-621C984D1F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC79C5A-972A-46D8-AC01-4B2445DD8DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="127">
   <si>
     <t>Name</t>
   </si>
@@ -400,6 +400,12 @@
   </si>
   <si>
     <t>Process_Name</t>
+  </si>
+  <si>
+    <t>Business_Exception_Mail_Subject</t>
+  </si>
+  <si>
+    <t>Required Fields are Missing</t>
   </si>
 </sst>
 </file>
@@ -804,7 +810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1019"/>
+  <dimension ref="A1:Z1020"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
@@ -1024,224 +1030,232 @@
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B21" t="s">
-        <v>98</v>
+        <v>125</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
+      </c>
+      <c r="B22" t="s">
+        <v>98</v>
       </c>
       <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C24" s="2"/>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="C25" s="2"/>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C26" s="2"/>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C27" s="2"/>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C28" s="2"/>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="C29" s="2"/>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C31" s="2"/>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="C32" s="2"/>
     </row>
     <row r="33" spans="1:3" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="C33" s="2"/>
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="C34" s="2"/>
     </row>
     <row r="35" spans="1:3" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="C35" s="2"/>
     </row>
     <row r="36" spans="1:3" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C36" s="2"/>
     </row>
     <row r="37" spans="1:3" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="C37" s="2"/>
     </row>
     <row r="38" spans="1:3" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C38" s="2"/>
     </row>
     <row r="39" spans="1:3" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B39" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>66</v>
       </c>
       <c r="C39" s="2"/>
     </row>
     <row r="40" spans="1:3" ht="14.25" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="B40" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="2"/>
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A46" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B46" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="47" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="48" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
@@ -2215,6 +2229,7 @@
     <row r="1017" ht="14.25" customHeight="1"/>
     <row r="1018" ht="14.25" customHeight="1"/>
     <row r="1019" ht="14.25" customHeight="1"/>
+    <row r="1020" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC79C5A-972A-46D8-AC01-4B2445DD8DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C05A58-EE77-45F9-BA8B-A30AB20A7CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="130">
   <si>
     <t>Name</t>
   </si>
@@ -402,10 +402,19 @@
     <t>Process_Name</t>
   </si>
   <si>
-    <t>Business_Exception_Mail_Subject</t>
-  </si>
-  <si>
-    <t>Required Fields are Missing</t>
+    <t>Missing_Fields_Header_File</t>
+  </si>
+  <si>
+    <t>One or More Required Fields are Missing</t>
+  </si>
+  <si>
+    <t>Business_Exception_Mail_Subject_Missing_fields</t>
+  </si>
+  <si>
+    <t>Business_Exception_Mail_Subject_Invalid_data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invalid or Duplicate Data Found </t>
   </si>
 </sst>
 </file>
@@ -810,7 +819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1020"/>
+  <dimension ref="A1:Z1022"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
@@ -1030,234 +1039,250 @@
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B22" t="s">
-        <v>98</v>
+        <v>127</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
+      </c>
+      <c r="B23" t="s">
+        <v>98</v>
       </c>
       <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C24" s="2"/>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C25" s="2"/>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="C26" s="2"/>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C27" s="2"/>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C28" s="2"/>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C29" s="2"/>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C31" s="2"/>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C32" s="2"/>
     </row>
     <row r="33" spans="1:3" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="C33" s="2"/>
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="C34" s="2"/>
     </row>
     <row r="35" spans="1:3" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="C35" s="2"/>
     </row>
     <row r="36" spans="1:3" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="C36" s="2"/>
     </row>
     <row r="37" spans="1:3" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" s="2"/>
     </row>
     <row r="38" spans="1:3" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="C38" s="2"/>
     </row>
     <row r="39" spans="1:3" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>66</v>
+        <v>125</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="C39" s="2"/>
     </row>
     <row r="40" spans="1:3" ht="14.25" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B40" t="s">
-        <v>67</v>
+        <v>63</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C40" s="2"/>
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="C41" s="2"/>
     </row>
     <row r="42" spans="1:3" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>77</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="B42" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42" s="2"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A47" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A48" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B48" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="48" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
     <row r="51" ht="14.25" customHeight="1"/>
@@ -2230,6 +2255,8 @@
     <row r="1018" ht="14.25" customHeight="1"/>
     <row r="1019" ht="14.25" customHeight="1"/>
     <row r="1020" ht="14.25" customHeight="1"/>
+    <row r="1021" ht="14.25" customHeight="1"/>
+    <row r="1022" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C05A58-EE77-45F9-BA8B-A30AB20A7CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9CD7B4-021A-4D43-86A8-BAC23CC66C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="136">
   <si>
     <t>Name</t>
   </si>
@@ -415,6 +415,24 @@
   </si>
   <si>
     <t xml:space="preserve">Invalid or Duplicate Data Found </t>
+  </si>
+  <si>
+    <t>IT_Team_Mail_Address_success</t>
+  </si>
+  <si>
+    <t>IT_Team_Mail_Address_missing</t>
+  </si>
+  <si>
+    <t>IT_Team_Mail_Address_failed</t>
+  </si>
+  <si>
+    <t>IT_Team_CC_Address_success</t>
+  </si>
+  <si>
+    <t>IT_Team_CC_Address_missing</t>
+  </si>
+  <si>
+    <t>IT_Team_CC_Address_failed</t>
   </si>
 </sst>
 </file>
@@ -819,7 +837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1022"/>
+  <dimension ref="A1:Z1028"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
@@ -931,374 +949,411 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B10" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="C10" s="4"/>
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" t="s">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="C11" s="4"/>
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B12" s="8">
-        <v>587</v>
+        <v>103</v>
+      </c>
+      <c r="B12" t="s">
+        <v>104</v>
       </c>
       <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:26">
       <c r="A13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:26" s="4" customFormat="1">
+      <c r="A14" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" s="4" customFormat="1">
+      <c r="A15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26">
+      <c r="A16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="8">
+        <v>587</v>
+      </c>
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="5">
-        <v>3123</v>
-      </c>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" s="2"/>
-    </row>
-    <row r="16" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A17" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C19" s="2"/>
+      <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>110</v>
+        <v>45</v>
+      </c>
+      <c r="B20" s="5">
+        <v>3123</v>
       </c>
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>129</v>
+        <v>51</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" t="s">
-        <v>98</v>
+        <v>56</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C24" s="2"/>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C25" s="2"/>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C26" s="2"/>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>47</v>
+        <v>129</v>
       </c>
       <c r="C27" s="2"/>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="C28" s="2"/>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>50</v>
+        <v>97</v>
+      </c>
+      <c r="B29" t="s">
+        <v>98</v>
       </c>
       <c r="C29" s="2"/>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="C31" s="2"/>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C32" s="2"/>
     </row>
     <row r="33" spans="1:3" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="C33" s="2"/>
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="C34" s="2"/>
     </row>
     <row r="35" spans="1:3" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="C35" s="2"/>
     </row>
     <row r="36" spans="1:3" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="C36" s="2"/>
     </row>
     <row r="37" spans="1:3" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C37" s="2"/>
     </row>
     <row r="38" spans="1:3" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C38" s="2"/>
     </row>
     <row r="39" spans="1:3" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C39" s="2"/>
     </row>
     <row r="40" spans="1:3" ht="14.25" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C40" s="2"/>
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>66</v>
+        <v>59</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="C41" s="2"/>
     </row>
     <row r="42" spans="1:3" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B42" t="s">
-        <v>67</v>
+        <v>61</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="C42" s="2"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" s="2"/>
     </row>
     <row r="44" spans="1:3" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>77</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C44" s="2"/>
     </row>
     <row r="45" spans="1:3" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>78</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="2"/>
     </row>
     <row r="46" spans="1:3" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>79</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" s="2"/>
     </row>
     <row r="47" spans="1:3" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>75</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="C47" s="2"/>
     </row>
     <row r="48" spans="1:3" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B48" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" s="2"/>
+    </row>
+    <row r="49" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A49" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A50" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A51" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A53" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A54" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B54" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="49" ht="14.25" customHeight="1"/>
-    <row r="50" ht="14.25" customHeight="1"/>
-    <row r="51" ht="14.25" customHeight="1"/>
-    <row r="52" ht="14.25" customHeight="1"/>
-    <row r="53" ht="14.25" customHeight="1"/>
-    <row r="54" ht="14.25" customHeight="1"/>
-    <row r="55" ht="14.25" customHeight="1"/>
-    <row r="56" ht="14.25" customHeight="1"/>
-    <row r="57" ht="14.25" customHeight="1"/>
-    <row r="58" ht="14.25" customHeight="1"/>
-    <row r="59" ht="14.25" customHeight="1"/>
-    <row r="60" ht="14.25" customHeight="1"/>
-    <row r="61" ht="14.25" customHeight="1"/>
-    <row r="62" ht="14.25" customHeight="1"/>
-    <row r="63" ht="14.25" customHeight="1"/>
-    <row r="64" ht="14.25" customHeight="1"/>
+    <row r="55" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="56" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="57" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="58" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="59" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="60" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="61" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="62" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="63" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="64" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="65" ht="14.25" customHeight="1"/>
     <row r="66" ht="14.25" customHeight="1"/>
     <row r="67" ht="14.25" customHeight="1"/>
@@ -2257,6 +2312,12 @@
     <row r="1020" ht="14.25" customHeight="1"/>
     <row r="1021" ht="14.25" customHeight="1"/>
     <row r="1022" ht="14.25" customHeight="1"/>
+    <row r="1023" ht="14.25" customHeight="1"/>
+    <row r="1024" ht="14.25" customHeight="1"/>
+    <row r="1025" ht="14.25" customHeight="1"/>
+    <row r="1026" ht="14.25" customHeight="1"/>
+    <row r="1027" ht="14.25" customHeight="1"/>
+    <row r="1028" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9CD7B4-021A-4D43-86A8-BAC23CC66C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83172A56-F67D-41AD-9E71-F81B785177B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="138">
   <si>
     <t>Name</t>
   </si>
@@ -433,13 +433,19 @@
   </si>
   <si>
     <t>IT_Team_CC_Address_failed</t>
+  </si>
+  <si>
+    <t>Fatima_Saha@gulfdrug.com</t>
+  </si>
+  <si>
+    <t>Sayeed_Ahmed@gulfdrug.com;Shariar@gulfdrug.com;Owais_Rashid@gulfdrug.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -483,6 +489,18 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -501,10 +519,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -523,8 +542,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -951,18 +973,27 @@
       <c r="A9" s="2" t="s">
         <v>133</v>
       </c>
+      <c r="B9" s="10" t="s">
+        <v>137</v>
+      </c>
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="2" t="s">
         <v>134</v>
       </c>
+      <c r="B10" s="10" t="s">
+        <v>137</v>
+      </c>
       <c r="C10" s="4"/>
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="B11" s="11" t="s">
+        <v>137</v>
+      </c>
       <c r="C11" s="4"/>
     </row>
     <row r="12" spans="1:26">
@@ -979,7 +1010,7 @@
         <v>130</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="C13" s="4"/>
     </row>
@@ -988,7 +1019,7 @@
         <v>131</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:26" s="4" customFormat="1">
@@ -996,7 +1027,7 @@
         <v>132</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:26">

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83172A56-F67D-41AD-9E71-F81B785177B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B2770E-2071-4EEF-BB76-1455F6960265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -523,7 +523,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -543,7 +543,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -991,7 +990,7 @@
       <c r="A11" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" t="s">
         <v>137</v>
       </c>
       <c r="C11" s="4"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B2770E-2071-4EEF-BB76-1455F6960265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50AB00B2-0132-496F-A71E-63396B16A402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50AB00B2-0132-496F-A71E-63396B16A402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F474AADA-4BA9-4AE8-B2A5-117AC9BA3F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="154">
   <si>
     <t>Name</t>
   </si>
@@ -439,13 +439,61 @@
   </si>
   <si>
     <t>Sayeed_Ahmed@gulfdrug.com;Shariar@gulfdrug.com;Owais_Rashid@gulfdrug.com</t>
+  </si>
+  <si>
+    <t>SAP_Web_link</t>
+  </si>
+  <si>
+    <t>https://hcm22preview.sapsf.com/</t>
+  </si>
+  <si>
+    <t>Company_id</t>
+  </si>
+  <si>
+    <t>gulfdrugesT1</t>
+  </si>
+  <si>
+    <t>SAP_User_name</t>
+  </si>
+  <si>
+    <t>SAP_Password</t>
+  </si>
+  <si>
+    <t>fatimasa</t>
+  </si>
+  <si>
+    <t>Today@1234</t>
+  </si>
+  <si>
+    <t>AlreadyExist_Status_path</t>
+  </si>
+  <si>
+    <t>AlreadyExist_Status_SheetName</t>
+  </si>
+  <si>
+    <t>C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\Output\Already_Exist\</t>
+  </si>
+  <si>
+    <t>Gulfdrug_AlreadyExist</t>
+  </si>
+  <si>
+    <t>FTP_Alreadyexistfolder</t>
+  </si>
+  <si>
+    <t>sf2or_pw_already_exist/</t>
+  </si>
+  <si>
+    <t>Home_link</t>
+  </si>
+  <si>
+    <t>https://hcm22preview.sapsf.com/sf/home</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -501,6 +549,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -523,7 +577,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -543,6 +597,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -858,7 +913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1028"/>
+  <dimension ref="A1:Z1032"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
@@ -1292,98 +1347,156 @@
     </row>
     <row r="45" spans="1:3" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="C45" s="2"/>
     </row>
     <row r="46" spans="1:3" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>63</v>
+        <v>147</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="C46" s="2"/>
     </row>
     <row r="47" spans="1:3" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>66</v>
+        <v>125</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="C47" s="2"/>
     </row>
     <row r="48" spans="1:3" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" s="2"/>
+    </row>
+    <row r="49" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A49" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C49" s="2"/>
+    </row>
+    <row r="50" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A50" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B50" t="s">
         <v>67</v>
       </c>
-      <c r="C48" s="2"/>
-    </row>
-    <row r="49" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A49" s="2" t="s">
+      <c r="C50" s="2"/>
+    </row>
+    <row r="51" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A51" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B51" s="7" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A50" s="2" t="s">
+    <row r="52" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A52" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B52" s="7" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A51" s="2" t="s">
+    <row r="53" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A53" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B53" s="7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A52" s="2" t="s">
+    <row r="54" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A54" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B54" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A53" s="2" t="s">
+    <row r="55" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A55" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A56" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B56" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A54" s="2" t="s">
+    <row r="57" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A57" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B57" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="56" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="57" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="58" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="59" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="60" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="61" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="62" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="63" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="64" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="58" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A58" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B58" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A59" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B59" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A60" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A61" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A62" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="64" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="65" ht="14.25" customHeight="1"/>
     <row r="66" ht="14.25" customHeight="1"/>
     <row r="67" ht="14.25" customHeight="1"/>
@@ -2348,6 +2461,10 @@
     <row r="1026" ht="14.25" customHeight="1"/>
     <row r="1027" ht="14.25" customHeight="1"/>
     <row r="1028" ht="14.25" customHeight="1"/>
+    <row r="1029" ht="14.25" customHeight="1"/>
+    <row r="1030" ht="14.25" customHeight="1"/>
+    <row r="1031" ht="14.25" customHeight="1"/>
+    <row r="1032" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Atominos Consulting\Documents\UiPath\Gulf Drug Process\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F474AADA-4BA9-4AE8-B2A5-117AC9BA3F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D0DC0C-631B-4D41-B6D5-95632F3C9E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -252,9 +252,6 @@
     <t>FTP_Path</t>
   </si>
   <si>
-    <t>incoming/</t>
-  </si>
-  <si>
     <t>sf2or_pw_input/</t>
   </si>
   <si>
@@ -282,9 +279,6 @@
     <t>Staging_Folder</t>
   </si>
   <si>
-    <t>welcome123</t>
-  </si>
-  <si>
     <t>Mail_ID</t>
   </si>
   <si>
@@ -459,12 +453,6 @@
     <t>SAP_Password</t>
   </si>
   <si>
-    <t>fatimasa</t>
-  </si>
-  <si>
-    <t>Today@1234</t>
-  </si>
-  <si>
     <t>AlreadyExist_Status_path</t>
   </si>
   <si>
@@ -487,6 +475,18 @@
   </si>
   <si>
     <t>https://hcm22preview.sapsf.com/sf/home</t>
+  </si>
+  <si>
+    <t>Today@12345</t>
+  </si>
+  <si>
+    <t>HCM_BOT_USER</t>
+  </si>
+  <si>
+    <t>welcome@1234</t>
+  </si>
+  <si>
+    <t>outgoing/</t>
   </si>
 </sst>
 </file>
@@ -577,7 +577,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -587,17 +587,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -917,19 +926,19 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
-    <col min="2" max="2" width="166.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="166.140625" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="81.42578125" customWidth="1"/>
     <col min="4" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="1"/>
@@ -960,7 +969,7 @@
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="7" t="s">
         <v>44</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -971,7 +980,6 @@
       <c r="A3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="2"/>
       <c r="C3" s="4" t="s">
         <v>32</v>
       </c>
@@ -980,7 +988,7 @@
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -989,124 +997,124 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="C5" s="4"/>
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>122</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>117</v>
+        <v>84</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="C7" s="4"/>
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B8" t="s">
-        <v>118</v>
+        <v>85</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="C8" s="4"/>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>137</v>
+        <v>131</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>135</v>
       </c>
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>137</v>
+        <v>132</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>135</v>
       </c>
       <c r="C10" s="4"/>
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>135</v>
-      </c>
-      <c r="B11" t="s">
-        <v>137</v>
       </c>
       <c r="C11" s="4"/>
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B12" t="s">
-        <v>104</v>
+        <v>101</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:26">
       <c r="A13" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B13" t="s">
-        <v>136</v>
+        <v>128</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:26" s="4" customFormat="1">
       <c r="A14" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B14" t="s">
-        <v>136</v>
+        <v>129</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:26" s="4" customFormat="1">
       <c r="A15" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B15" t="s">
-        <v>136</v>
+        <v>130</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B16" t="s">
-        <v>119</v>
+        <v>86</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B17" t="s">
-        <v>89</v>
+        <v>88</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" s="8">
+        <v>89</v>
+      </c>
+      <c r="B18" s="7">
         <v>587</v>
       </c>
       <c r="C18" s="4"/>
@@ -1115,8 +1123,8 @@
       <c r="A19" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>105</v>
+      <c r="B19" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="C19" s="4"/>
     </row>
@@ -1124,8 +1132,8 @@
       <c r="A20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="5">
-        <v>3123</v>
+      <c r="B20" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="C20" s="2"/>
     </row>
@@ -1133,8 +1141,8 @@
       <c r="A21" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>85</v>
+      <c r="B21" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="C21" s="2"/>
     </row>
@@ -1142,8 +1150,8 @@
       <c r="A22" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>106</v>
+      <c r="B22" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="C22" s="2"/>
     </row>
@@ -1151,17 +1159,17 @@
       <c r="A23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>107</v>
+      <c r="B23" s="7" t="s">
+        <v>105</v>
       </c>
       <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>108</v>
+        <v>83</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>106</v>
       </c>
       <c r="C24" s="2"/>
     </row>
@@ -1169,71 +1177,71 @@
       <c r="A25" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>109</v>
+      <c r="B25" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="C25" s="2"/>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>110</v>
+        <v>93</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>108</v>
       </c>
       <c r="C26" s="2"/>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>127</v>
       </c>
       <c r="C27" s="2"/>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="C28" s="2"/>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B29" t="s">
-        <v>98</v>
+        <v>95</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="C29" s="2"/>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>111</v>
+        <v>94</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>99</v>
       </c>
       <c r="C31" s="2"/>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>112</v>
+        <v>97</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="C32" s="2"/>
     </row>
@@ -1241,7 +1249,7 @@
       <c r="A33" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C33" s="2"/>
@@ -1250,7 +1258,7 @@
       <c r="A34" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="7" t="s">
         <v>55</v>
       </c>
       <c r="C34" s="2"/>
@@ -1259,7 +1267,7 @@
       <c r="A35" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="7" t="s">
         <v>50</v>
       </c>
       <c r="C35" s="2"/>
@@ -1268,17 +1276,17 @@
       <c r="A36" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="7" t="s">
         <v>53</v>
       </c>
       <c r="C36" s="2"/>
     </row>
     <row r="37" spans="1:3" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>113</v>
+        <v>100</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="C37" s="2"/>
     </row>
@@ -1286,8 +1294,8 @@
       <c r="A38" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>114</v>
+      <c r="B38" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="C38" s="2"/>
     </row>
@@ -1295,8 +1303,8 @@
       <c r="A39" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>115</v>
+      <c r="B39" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="C39" s="2"/>
     </row>
@@ -1304,8 +1312,8 @@
       <c r="A40" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>82</v>
+      <c r="B40" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="C40" s="2"/>
     </row>
@@ -1313,8 +1321,8 @@
       <c r="A41" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>116</v>
+      <c r="B41" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C41" s="2"/>
     </row>
@@ -1322,53 +1330,53 @@
       <c r="A42" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>83</v>
+      <c r="B42" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="C42" s="2"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="C43" s="2"/>
     </row>
     <row r="44" spans="1:3" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="C44" s="2"/>
     </row>
     <row r="45" spans="1:3" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>144</v>
       </c>
       <c r="C45" s="2"/>
     </row>
     <row r="46" spans="1:3" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>149</v>
+        <v>143</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="C46" s="2"/>
     </row>
     <row r="47" spans="1:3" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="C47" s="2"/>
     </row>
@@ -1376,7 +1384,7 @@
       <c r="A48" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="7" t="s">
         <v>64</v>
       </c>
       <c r="C48" s="2"/>
@@ -1385,7 +1393,7 @@
       <c r="A49" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C49" s="2"/>
@@ -1394,7 +1402,7 @@
       <c r="A50" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="7" t="s">
         <v>67</v>
       </c>
       <c r="C50" s="2"/>
@@ -1403,96 +1411,96 @@
       <c r="A51" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>76</v>
+      <c r="B51" s="9" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B52" s="7" t="s">
-        <v>77</v>
+      <c r="B52" s="9" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B53" s="7" t="s">
-        <v>78</v>
+      <c r="B53" s="9" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B54" s="7" t="s">
-        <v>79</v>
+      <c r="B54" s="9" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>151</v>
+        <v>146</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B56" s="7" t="s">
-        <v>75</v>
+      <c r="B56" s="9" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B57" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="B57" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B58" t="s">
-        <v>139</v>
+        <v>136</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="14.25" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B59" t="s">
-        <v>153</v>
+        <v>148</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B60" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B61" s="11" t="s">
-        <v>144</v>
+        <v>140</v>
+      </c>
+      <c r="B61" s="10">
+        <v>2500</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B62" s="11" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="14.25" customHeight="1"/>
